--- a/artfynd/A 48879-2022 artfynd.xlsx
+++ b/artfynd/A 48879-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48879-2022 artfynd.xlsx
+++ b/artfynd/A 48879-2022 artfynd.xlsx
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1232055</v>
+        <v>133132568</v>
       </c>
       <c r="B2" t="n">
-        <v>85453</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3639</v>
+        <v>219933</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rutspindling</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius ionophyllus</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsbrohammar, Nrk</t>
+          <t>Åsbrohammar 1, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502448.0863339639</v>
+        <v>502531</v>
       </c>
       <c r="R2" t="n">
-        <v>6538619.356959301</v>
+        <v>6538016</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-08-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-08-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Källa: Svampar i Närke - En sammanställning av svampfynd 1977-2008 av Karl Gustaf Nilsson. Länsstyrelsen i Örebro län, publ.nr: 2008:32</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,36 +766,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktig granskog</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karl Gustaf Nilsson</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl Gustaf Nilsson</t>
+          <t>Elisabet Hultberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 48879-2022 artfynd.xlsx
+++ b/artfynd/A 48879-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,8 +787,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133132568</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>